--- a/files/九龙-何文田-太子道西233号.xlsx
+++ b/files/九龙-何文田-太子道西233号.xlsx
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>63780000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>41686</v>
+        <v>41714</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>31170000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>30000</v>
+        <v>30029</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>29800000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>28681</v>
+        <v>28709</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>29469000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>28363</v>
+        <v>28390</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>29200000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>28104</v>
+        <v>28131</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>28488000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>27419</v>
+        <v>27445</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>25088000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>24146</v>
+        <v>24170</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>28680000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>27603</v>
+        <v>27630</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>25000000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>24062</v>
+        <v>24085</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>26500000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>25505</v>
+        <v>25530</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>24350000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>23436</v>
+        <v>23459</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>8150000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>21676</v>
+        <v>21733</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>8090000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>21516</v>
+        <v>21573</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>17830000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>22040</v>
+        <v>22012</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>8060000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>21436</v>
+        <v>21493</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5888,9 +5888,9 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 1530呎 (4+房)
+          <t>B | 1529呎 (4+房)
 $6378万
-$41,686/呎
+$41,714/呎
 (25年-01月-23日)</t>
         </is>
       </c>
@@ -5908,9 +5908,9 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $3117万
-$30,000/呎
+$30,029/呎
 (25年-02月-21日)</t>
         </is>
       </c>
@@ -5957,9 +5957,9 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2980万
-$28,681/呎
+$28,709/呎
 (24年-12月-30日)</t>
         </is>
       </c>
@@ -6006,9 +6006,9 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2947万
-$28,363/呎
+$28,390/呎
 (24年-12月-27日)</t>
         </is>
       </c>
@@ -6055,9 +6055,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2920万
-$28,104/呎
+$28,131/呎
 (25年-01月-09日)</t>
         </is>
       </c>
@@ -6104,9 +6104,9 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2849万
-$27,419/呎
+$27,445/呎
 (24年-12月-23日)</t>
         </is>
       </c>
@@ -6153,9 +6153,9 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2509万
-$24,146/呎
+$24,170/呎
 (25年-02月-17日)</t>
         </is>
       </c>
@@ -6202,9 +6202,9 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2868万
-$27,603/呎
+$27,630/呎
 (25年-09月-09日)</t>
         </is>
       </c>
@@ -6251,9 +6251,9 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2500万
-$24,062/呎
+$24,085/呎
 (25年-09月-18日)</t>
         </is>
       </c>
@@ -6300,9 +6300,9 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2650万
-$25,505/呎
+$25,530/呎
 (25年-02月-20日)</t>
         </is>
       </c>
@@ -6349,9 +6349,9 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 1039呎 (4+房)
+          <t>A | 1038呎 (4+房)
 $2435万
-$23,436/呎
+$23,459/呎
 (24年-12月-28日)</t>
         </is>
       </c>
@@ -6406,9 +6406,9 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 376呎 (2房)
+          <t>B | 375呎 (2房)
 $815万
-$21,676/呎
+$21,733/呎
 (25年-07月-16日)</t>
         </is>
       </c>
@@ -6469,9 +6469,9 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>B | 376呎 (2房)
+          <t>B | 375呎 (2房)
 $809万
-$21,516/呎
+$21,573/呎
 (25年-06月-16日)</t>
         </is>
       </c>
@@ -6532,9 +6532,9 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>B | 376呎 (2房)
+          <t>B | 375呎 (2房)
 $806万
-$21,436/呎
+$21,493/呎
 (25年-05月-22日)</t>
         </is>
       </c>
@@ -6556,9 +6556,9 @@
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>E | 809呎 (3房)
+          <t>E | 810呎 (3房)
 $1783万
-$22,040/呎
+$22,012/呎
 (25年-08月-27日)</t>
         </is>
       </c>
